--- a/files/lamc_sample_enrollment.xlsx
+++ b/files/lamc_sample_enrollment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="programs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="sections" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="catalog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="programs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/files/lamc_sample_enrollment.xlsx
+++ b/files/lamc_sample_enrollment.xlsx
@@ -18276,7 +18276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18674,31 +18674,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AS-T-BUS</t>
+          <t>AS-T-CSCI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Business Administration AS-T</t>
+          <t>Computer Science AS-T</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CSU GE-Breadth</t>
+          <t>IGETC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ACCTG 1</t>
+          <t>PSYC 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ACCTG 2</t>
+          <t>ACCTG 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ECON 1</t>
+          <t>ACCTG 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -18758,7 +18758,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -18779,7 +18779,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ECON 2</t>
+          <t>ECON 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -18788,7 +18788,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BUS 1</t>
+          <t>ECON 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -18818,7 +18818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BUS 5</t>
+          <t>BUS 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -18848,7 +18848,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MATH 236</t>
+          <t>BUS 5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ENGL 101</t>
+          <t>MATH 236</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -18908,7 +18908,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COMM 101</t>
+          <t>ENGL 101</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -18938,28 +18938,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AS-T-BIOL</t>
+          <t>AS-T-BUS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biology AS-T</t>
+          <t>Business Administration AS-T</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IGETC</t>
+          <t>CSU GE-Breadth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BIOL 6</t>
+          <t>COMM 101</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -18968,67 +18968,67 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AS-T-BIOL</t>
+          <t>AS-T-BUS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Biology AS-T</t>
+          <t>Business Administration AS-T</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IGETC</t>
+          <t>CSU GE-Breadth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BIOL 7</t>
+          <t>HIST 11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AS-T-BIOL</t>
+          <t>AS-T-BUS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Biology AS-T</t>
+          <t>Business Administration AS-T</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IGETC</t>
+          <t>CSU GE-Breadth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHEM 101</t>
+          <t>PSYC 1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CHEM 102</t>
+          <t>BIOL 6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -19058,7 +19058,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CHEM 211</t>
+          <t>BIOL 7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -19088,7 +19088,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -19109,7 +19109,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CHEM 212</t>
+          <t>CHEM 101</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -19118,7 +19118,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MATH 245</t>
+          <t>CHEM 102</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -19148,7 +19148,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PHYS 101</t>
+          <t>CHEM 211</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENGL 101</t>
+          <t>CHEM 212</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -19208,18 +19208,18 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AS-T-ENGR</t>
+          <t>AS-T-BIOL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Engineering AS-T</t>
+          <t>Biology AS-T</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ENGR 101</t>
+          <t>MATH 245</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -19244,12 +19244,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AS-T-ENGR</t>
+          <t>AS-T-BIOL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Engineering AS-T</t>
+          <t>Biology AS-T</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ENGR 102</t>
+          <t>PHYS 101</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -19274,12 +19274,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AS-T-ENGR</t>
+          <t>AS-T-BIOL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Engineering AS-T</t>
+          <t>Biology AS-T</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ENGR 103</t>
+          <t>ENGL 101</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -19298,18 +19298,18 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AS-T-ENGR</t>
+          <t>AS-T-BIOL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Engineering AS-T</t>
+          <t>Biology AS-T</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -19319,27 +19319,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MATH 245</t>
+          <t>HIST 11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AS-T-ENGR</t>
+          <t>AS-T-BIOL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Engineering AS-T</t>
+          <t>Biology AS-T</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -19349,16 +19349,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PHYS 101</t>
+          <t>COMM 101</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -19379,15 +19379,165 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>ENGR 101</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AS-T-ENGR</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Engineering AS-T</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IGETC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ENGR 102</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AS-T-ENGR</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Engineering AS-T</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>IGETC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ENGR 103</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AS-T-ENGR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Engineering AS-T</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IGETC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MATH 245</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AS-T-ENGR</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Engineering AS-T</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IGETC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PHYS 101</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AS-T-ENGR</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Engineering AS-T</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IGETC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>ENGL 101</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F42" t="n">
         <v>1</v>
       </c>
     </row>
